--- a/metrics/Metrics_Ablation_Study_VPD_DT.xlsx
+++ b/metrics/Metrics_Ablation_Study_VPD_DT.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U4"/>
+  <dimension ref="A1:AS4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,60 +471,180 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
+          <t>MAE_constant</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>MedAE_constant</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>MSE_constant</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>RMSE_constant</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>R2_constant</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Pearson_constant</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Spearman_constant</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Kendall_constant</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>MAE_stepwise</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>MedAE_stepwise</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>MSE_stepwise</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>RMSE_stepwise</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>R2_stepwise</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>Pearson_stepwise</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>Spearman_stepwise</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Kendall_stepwise</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>MAE_dynamic</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>MedAE_dynamic</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>MSE_dynamic</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>RMSE_dynamic</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>R2_dynamic</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>Pearson_dynamic</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>Spearman_dynamic</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>Kendall_dynamic</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
           <t>Int_Conf_R2</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>Int_Conf_RMSE</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>Int_Conf_Pearson</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>Int_Conf_Spearman</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>Int_Conf_Kendall</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>Int_Conf_MAE</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>Int_Conf_MedAE</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>Target</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>Model</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>Lag</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>Max_Step</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>Pred_Step</t>
         </is>
@@ -535,67 +655,139 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.318751088944888</v>
+        <v>2.292639806771999</v>
       </c>
       <c r="C2" t="n">
-        <v>2.429814933077889</v>
+        <v>2.204310925875295</v>
       </c>
       <c r="D2" t="n">
-        <v>7.20644088489486</v>
+        <v>6.858687709308865</v>
       </c>
       <c r="E2" t="n">
-        <v>2.684481492745826</v>
+        <v>2.61890964130282</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9096165364865286</v>
+        <v>0.9229651716753031</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9540483106143308</v>
+        <v>0.9610271823769663</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9555296509325804</v>
+        <v>0.9617944381720795</v>
       </c>
       <c r="I2" t="n">
-        <v>0.8223292248971428</v>
+        <v>0.8388560382452599</v>
       </c>
       <c r="J2" t="n">
-        <v>0.007578846427154617</v>
+        <v>3.004256181566469</v>
       </c>
       <c r="K2" t="n">
-        <v>0.1093453707675855</v>
+        <v>3.16007980808985</v>
       </c>
       <c r="L2" t="n">
-        <v>0.4776511936198127</v>
+        <v>10.47519286875512</v>
       </c>
       <c r="M2" t="n">
-        <v>0.4792293624279093</v>
+        <v>3.236540262186633</v>
       </c>
       <c r="N2" t="n">
-        <v>0.4074378301765236</v>
+        <v>0.8874610253162531</v>
       </c>
       <c r="O2" t="n">
-        <v>0.1108002288046503</v>
+        <v>0.964417556826193</v>
       </c>
       <c r="P2" t="n">
-        <v>0.1532476561779363</v>
-      </c>
-      <c r="Q2" t="inlineStr">
+        <v>0.9657148264130884</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0.8572077668446897</v>
+      </c>
+      <c r="R2" t="n">
+        <v>2.304138619812521</v>
+      </c>
+      <c r="S2" t="n">
+        <v>2.319562093355825</v>
+      </c>
+      <c r="T2" t="n">
+        <v>6.460536519049504</v>
+      </c>
+      <c r="U2" t="n">
+        <v>2.541758548534755</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0.9127854824465053</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0.9556277496984192</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0.948582979053284</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0.8096532931821445</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>2.027027947020972</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.848382056877415</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>5.780511334788524</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>2.404269397299005</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>0.9311945711288714</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>0.9699952933785537</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>0.968880141030068</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>0.8598154521349296</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>0.01196686443844425</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>0.1542320412452043</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>0.00649886819179496</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>0.007978806027978624</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>0.01687916966527153</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>0.1533351567631358</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>0.1954707008323068</v>
+      </c>
+      <c r="AO2" t="inlineStr">
         <is>
           <t>RSL</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="AP2" t="inlineStr">
         <is>
           <t>RF</t>
         </is>
       </c>
-      <c r="S2" t="n">
+      <c r="AQ2" t="n">
         <v>3</v>
       </c>
-      <c r="T2" t="n">
+      <c r="AR2" t="n">
         <v>1</v>
       </c>
-      <c r="U2" t="n">
+      <c r="AS2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -604,67 +796,139 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0.3501722861193783</v>
+        <v>0.3430237016259675</v>
       </c>
       <c r="C3" t="n">
-        <v>0.2313554117952833</v>
+        <v>0.2136972599164961</v>
       </c>
       <c r="D3" t="n">
-        <v>0.2402211922037543</v>
+        <v>0.2352969792631335</v>
       </c>
       <c r="E3" t="n">
-        <v>0.4901236499127075</v>
+        <v>0.4850741997500315</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9571584856489497</v>
+        <v>0.9624593342913957</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9802604699102607</v>
+        <v>0.9831431072187258</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9846185127603446</v>
+        <v>0.9848525224558693</v>
       </c>
       <c r="I3" t="n">
-        <v>0.8944462669437844</v>
+        <v>0.8986989546713475</v>
       </c>
       <c r="J3" t="n">
-        <v>0.006835853553218807</v>
+        <v>0.2049631236802985</v>
       </c>
       <c r="K3" t="n">
-        <v>0.03852894045060137</v>
+        <v>0.2043097213252869</v>
       </c>
       <c r="L3" t="n">
-        <v>0.4905553721907416</v>
+        <v>0.05708860161339015</v>
       </c>
       <c r="M3" t="n">
-        <v>0.4908238028799279</v>
+        <v>0.2389322113349101</v>
       </c>
       <c r="N3" t="n">
-        <v>0.4424139930421337</v>
+        <v>0.9897592695754877</v>
       </c>
       <c r="O3" t="n">
-        <v>0.02393387744971773</v>
+        <v>0.9956264833363536</v>
       </c>
       <c r="P3" t="n">
-        <v>0.0220452984068667</v>
-      </c>
-      <c r="Q3" t="inlineStr">
+        <v>0.9927388702723987</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0.9438011705562938</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0.2301462760799894</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0.1835908376068771</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0.1047114442433069</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0.3235914773959704</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0.964585780854877</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0.9872153539880809</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0.9873863952692737</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0.9111074451506919</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>0.46039428070795</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>0.3203364898401253</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.3778038151145071</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>0.614657477880573</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0.9456996117571147</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>0.9824565903966473</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>0.9863310651847248</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>0.903493139748488</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>0.007319292306750269</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>0.04485926100928692</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>0.003231245720045128</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>0.004216948578980806</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>0.01363117037573286</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>0.03485074081913581</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>0.03893776726637078</v>
+      </c>
+      <c r="AO3" t="inlineStr">
         <is>
           <t>WL</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="AP3" t="inlineStr">
         <is>
           <t>RF</t>
         </is>
       </c>
-      <c r="S3" t="n">
+      <c r="AQ3" t="n">
         <v>3</v>
       </c>
-      <c r="T3" t="n">
+      <c r="AR3" t="n">
         <v>1</v>
       </c>
-      <c r="U3" t="n">
+      <c r="AS3" t="n">
         <v>1</v>
       </c>
     </row>
@@ -673,67 +937,139 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.129077550861066</v>
+        <v>1.117736884979234</v>
       </c>
       <c r="C4" t="n">
-        <v>0.6959857131601868</v>
+        <v>0.6355502808710538</v>
       </c>
       <c r="D4" t="n">
-        <v>2.786455547786266</v>
+        <v>2.842340085324936</v>
       </c>
       <c r="E4" t="n">
-        <v>1.669267967639188</v>
+        <v>1.685924104260015</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9559995032833061</v>
+        <v>0.9597949896406676</v>
       </c>
       <c r="G4" t="n">
-        <v>0.977794902844669</v>
+        <v>0.9797006919907868</v>
       </c>
       <c r="H4" t="n">
-        <v>0.9784326996752098</v>
+        <v>0.9765175831715879</v>
       </c>
       <c r="I4" t="n">
-        <v>0.8795445693876508</v>
+        <v>0.8786242845555439</v>
       </c>
       <c r="J4" t="n">
-        <v>0.006842657986113443</v>
+        <v>1.318536417073424</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1338573022843977</v>
+        <v>0.9690892046663251</v>
       </c>
       <c r="L4" t="n">
-        <v>0.4903943001700464</v>
+        <v>3.061498855185542</v>
       </c>
       <c r="M4" t="n">
-        <v>0.4864490521181739</v>
+        <v>1.749713935243571</v>
       </c>
       <c r="N4" t="n">
-        <v>0.4326827840428452</v>
+        <v>0.9636414020619989</v>
       </c>
       <c r="O4" t="n">
-        <v>0.09621144919029001</v>
+        <v>0.9834152815960824</v>
       </c>
       <c r="P4" t="n">
-        <v>0.1140268486195654</v>
-      </c>
-      <c r="Q4" t="inlineStr">
+        <v>0.9828424944302939</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0.9182124021262483</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.183594321925111</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0.6080577571002987</v>
+      </c>
+      <c r="T4" t="n">
+        <v>3.628106225032752</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1.904758836449578</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0.9110819320140665</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0.9586449667601696</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0.9539802199426386</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0.8426610870480852</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>1.005530976944131</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>0.6162730994353947</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>2.295082664392461</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>1.514953023823663</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0.9706100116235975</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>0.9860075771237604</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>0.981940600950938</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>0.8928540473968114</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>0.01102007333408006</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>0.2232341935426785</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>0.005619365631386097</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>0.006671764399367841</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>0.01518323255577736</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>0.1456172412718004</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>0.1193020017155475</v>
+      </c>
+      <c r="AO4" t="inlineStr">
         <is>
           <t>DI</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="AP4" t="inlineStr">
         <is>
           <t>RF</t>
         </is>
       </c>
-      <c r="S4" t="n">
+      <c r="AQ4" t="n">
         <v>3</v>
       </c>
-      <c r="T4" t="n">
+      <c r="AR4" t="n">
         <v>1</v>
       </c>
-      <c r="U4" t="n">
+      <c r="AS4" t="n">
         <v>1</v>
       </c>
     </row>
